--- a/271025_Results_Med/output/diccionario_med.xlsx
+++ b/271025_Results_Med/output/diccionario_med.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3449,6 +3449,40 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>p39_lugar_agregado_mod</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Variable dicotómica: en su modo de transporte o en otro lugar</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Módulo 4: Experiencias de acoso, inseguridad y VBG</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>p38p38_dummy</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Dummy: 1 si vivió al menos una situación de acoso/inseguridad, 0 si no vivió ninguna</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Módulo 4: Experiencias de acoso, inseguridad y VBG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
